--- a/measurements/30/Filled_2D_sections/coronal/week30_coronal_Batch_Allmarks.xlsx
+++ b/measurements/30/Filled_2D_sections/coronal/week30_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,107 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +601,76 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.635633551457466</v>
+        <v>2529.365079365079</v>
       </c>
       <c r="D2" t="n">
-        <v>15.72051685030867</v>
+        <v>306.9243766012646</v>
       </c>
       <c r="E2" t="n">
-        <v>11.46071681452961</v>
+        <v>223.756852093197</v>
       </c>
       <c r="F2" t="n">
         <v>1.371687051055882</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3374105187391221</v>
+        <v>0.3374105187391222</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6774009146341463</v>
+        <v>2.416294642857143</v>
       </c>
       <c r="J2" t="n">
-        <v>1.069455030487805</v>
+        <v>20.87983630952381</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8734279725609757</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>7.691060799319728</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20.87983630952381</v>
+      </c>
+      <c r="N2" t="n">
+        <v>13.22544642857143</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6.475074404761904</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5.128348214285714</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.048735119047619</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.663690476190476</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.416294642857143</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>6.671609161213564</v>
+      <c r="AH2" s="2" t="n">
+        <v>2543.078231292517</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +681,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.678762641284949</v>
+        <v>2545.804988662131</v>
       </c>
       <c r="D3" t="n">
-        <v>15.68112117197455</v>
+        <v>306.155222881408</v>
       </c>
       <c r="E3" t="n">
-        <v>11.54990838213665</v>
+        <v>225.4982112702869</v>
       </c>
       <c r="F3" t="n">
         <v>1.357683598272289</v>
@@ -572,24 +700,57 @@
         <v>0.3413120739493499</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6466272865853658</v>
+        <v>2.369791666666667</v>
       </c>
       <c r="J3" t="n">
-        <v>1.064405487804878</v>
+        <v>20.78125</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8555163871951219</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>7.554474914965986</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20.78125</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12.62462797619048</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6.075148809523809</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6.006324404761904</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.552083333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.472098214285714</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.369791666666667</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>15.74022341792176</v>
+      <c r="AH3" s="2" t="n">
+        <v>307.3091238737106</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +761,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.721594289113623</v>
+        <v>2562.131519274376</v>
       </c>
       <c r="D4" t="n">
-        <v>15.86787370646872</v>
+        <v>309.8013437929607</v>
       </c>
       <c r="E4" t="n">
-        <v>11.62481249541771</v>
+        <v>226.9606249105363</v>
       </c>
       <c r="F4" t="n">
         <v>1.365000400025682</v>
@@ -619,24 +780,57 @@
         <v>0.3354630480905141</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>0.649390243902439</v>
+        <v>2.555803571428571</v>
       </c>
       <c r="J4" t="n">
-        <v>1.034203506097561</v>
+        <v>20.19159226190476</v>
       </c>
       <c r="K4" t="n">
-        <v>0.841796875</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>7.607621173469385</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20.19159226190476</v>
+      </c>
+      <c r="N4" t="n">
+        <v>12.67857142857143</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.95610119047619</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5.697544642857142</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.491443452380952</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.682291666666667</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.555803571428571</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>11.62349758918693</v>
+      <c r="AH4" s="2" t="n">
+        <v>226.9349529317447</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +841,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.732897085068412</v>
+        <v>2566.439909297052</v>
       </c>
       <c r="D5" t="n">
-        <v>15.87624306795074</v>
+        <v>309.9647456123715</v>
       </c>
       <c r="E5" t="n">
-        <v>11.70216789478209</v>
+        <v>228.4708969933646</v>
       </c>
       <c r="F5" t="n">
         <v>1.356692470207152</v>
@@ -666,23 +860,53 @@
         <v>0.335672962416705</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.649390243902439</v>
+        <v>2.325148809523809</v>
       </c>
       <c r="J5" t="n">
-        <v>1.007145579268293</v>
+        <v>19.66331845238095</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8282679115853658</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>8.183283730158729</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>19.66331845238095</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12.67857142857143</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5.848214285714286</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.334449404761905</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.325148809523809</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AH5" s="2" t="n">
         <v>1.354150437848181</v>
       </c>
     </row>
@@ -694,17 +918,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.755205234979179</v>
+        <v>2574.943310657596</v>
       </c>
       <c r="D6" t="n">
-        <v>16.03687203802713</v>
+        <v>313.1008350281488</v>
       </c>
       <c r="E6" t="n">
-        <v>11.6878804462712</v>
+        <v>228.1919515700567</v>
       </c>
       <c r="F6" t="n">
         <v>1.372094120208374</v>
@@ -713,23 +937,56 @@
         <v>0.3300723038153109</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.650438262195122</v>
+        <v>1.078869047619047</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9963795731707318</v>
+        <v>19.453125</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8234089176829269</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>7.250744047619047</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>19.453125</v>
+      </c>
+      <c r="N6" t="n">
+        <v>12.69903273809524</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6.73735119047619</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.386904761904762</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.840401785714286</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.559523809523809</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.078869047619047</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AH6" s="2" t="n">
         <v>0.3384914185912697</v>
       </c>
     </row>
@@ -741,43 +998,76 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.775133848899465</v>
+        <v>2582.539682539682</v>
       </c>
       <c r="D7" t="n">
-        <v>15.99054290608662</v>
+        <v>312.1963138807387</v>
       </c>
       <c r="E7" t="n">
-        <v>11.72482481235411</v>
+        <v>228.9132463364374</v>
       </c>
       <c r="F7" t="n">
-        <v>1.363819345875245</v>
+        <v>1.363819345875244</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3329671014236322</v>
+        <v>0.3329671014236323</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6501524390243902</v>
+        <v>1.395089285714286</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9846608231707318</v>
+        <v>19.22433035714286</v>
       </c>
       <c r="K7" t="n">
-        <v>0.817406631097561</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>7.235065901360544</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19.22433035714286</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12.69345238095238</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6.510416666666666</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.159970238095238</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.048735119047619</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.613467261904762</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.395089285714286</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>2.35</v>
+      <c r="AH7" s="2" t="n">
+        <v>7.65</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1078,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.790303390838787</v>
+        <v>2588.321995464853</v>
       </c>
       <c r="D8" t="n">
-        <v>15.98809152696191</v>
+        <v>312.1484536216373</v>
       </c>
       <c r="E8" t="n">
-        <v>11.82830383137959</v>
+        <v>230.9335509936015</v>
       </c>
       <c r="F8" t="n">
         <v>1.35168082887309</v>
@@ -807,24 +1097,60 @@
         <v>0.3338149566386344</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6359565548780488</v>
+        <v>1.687127976190476</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9690358231707318</v>
+        <v>18.91927083333333</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8024961890243902</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>6.623651413690475</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18.91927083333333</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12.41629464285714</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6.03422619047619</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.645461309523809</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.755580357142857</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.451636904761905</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.079613095238095</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.687127976190476</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6219655106707317</v>
+      <c r="AH8" s="2" t="n">
+        <v>1.575985863095238</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1161,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.83224271267103</v>
+        <v>2604.308390022676</v>
       </c>
       <c r="D9" t="n">
-        <v>15.77521542804997</v>
+        <v>307.992301214309</v>
       </c>
       <c r="E9" t="n">
-        <v>11.76523587180347</v>
+        <v>229.702224163782</v>
       </c>
       <c r="F9" t="n">
         <v>1.340832908064071</v>
@@ -854,24 +1180,60 @@
         <v>0.345002746686017</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6392911585365854</v>
+        <v>1.616443452380952</v>
       </c>
       <c r="J9" t="n">
-        <v>0.96875</v>
+        <v>18.91369047619047</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8040205792682926</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>6.880580357142856</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>18.91369047619047</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12.48139880952381</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6.614583333333333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5.535714285714286</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.60751488095238</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.797619047619047</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.477678571428571</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.616443452380952</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.9249428353658538</v>
+      <c r="AH9" s="2" t="n">
+        <v>18.05840773809523</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1244,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.823914336704343</v>
+        <v>2601.133786848072</v>
       </c>
       <c r="D10" t="n">
-        <v>16.14525378041151</v>
+        <v>315.21685952232</v>
       </c>
       <c r="E10" t="n">
-        <v>11.75931780803494</v>
+        <v>229.5866810140155</v>
       </c>
       <c r="F10" t="n">
         <v>1.372975375270471</v>
@@ -901,24 +1263,60 @@
         <v>0.3289680182267146</v>
       </c>
       <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.683407738095238</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.91927083333333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.244466145833334</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.5353467987804879</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.9690358231707318</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.7069359756097562</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>18.91927083333333</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12.03497023809524</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10.45200892857143</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.553199404761904</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.697916666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.797619047619047</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.817336309523809</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.683407738095238</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.759057418699187</v>
+      <c r="AH10" s="2" t="n">
+        <v>7.333622685185185</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1327,76 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.798036882807853</v>
+        <v>2591.269841269841</v>
       </c>
       <c r="D11" t="n">
-        <v>16.03830802149889</v>
+        <v>313.1288708959307</v>
       </c>
       <c r="E11" t="n">
-        <v>11.73911227540272</v>
+        <v>229.1921920435769</v>
       </c>
       <c r="F11" t="n">
         <v>1.366228352300914</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3321056625210011</v>
+        <v>0.332105662521001</v>
       </c>
       <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.789434523809524</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.41703869047619</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.48837425595238</v>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.5369664634146342</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.9433117378048781</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.700266768292683</v>
+      <c r="M11" t="n">
+        <v>18.41703869047619</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12.11495535714286</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10.48363095238095</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9.536830357142856</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.789434523809524</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.777157738095238</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.338634672619047</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1407,76 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.802498512790006</v>
+        <v>2592.97052154195</v>
       </c>
       <c r="D12" t="n">
-        <v>16.07626772799143</v>
+        <v>313.8699889750708</v>
       </c>
       <c r="E12" t="n">
-        <v>11.71053732313761</v>
+        <v>228.6343001184009</v>
       </c>
       <c r="F12" t="n">
         <v>1.372803594266169</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3307560975386679</v>
+        <v>0.3307560975386677</v>
       </c>
       <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.768973214285714</v>
+      </c>
+      <c r="J12" t="n">
+        <v>18.40959821428571</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.499767485119047</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.555640243902439</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.9429306402439025</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.7058561991869919</v>
+      <c r="M12" t="n">
+        <v>18.40959821428571</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.08519345238095</v>
+      </c>
+      <c r="O12" t="n">
+        <v>10.84821428571428</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9.503348214285714</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.768973214285714</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.659970238095238</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.287946428571428</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>18.05840773809523</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1487,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.78108268887567</v>
+        <v>2584.807256235827</v>
       </c>
       <c r="D13" t="n">
-        <v>16.10484270642444</v>
+        <v>314.4278814111437</v>
       </c>
       <c r="E13" t="n">
-        <v>11.65583877737929</v>
+        <v>227.5663761297862</v>
       </c>
       <c r="F13" t="n">
         <v>1.381697449151357</v>
@@ -1026,16 +1506,60 @@
         <v>0.3285458072270827</v>
       </c>
       <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.356026785714286</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18.41517857142857</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.513950892857141</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.5817454268292683</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.9432164634146342</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.7036966463414634</v>
+      <c r="M13" t="n">
+        <v>18.41517857142857</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11.44345238095238</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11.3578869047619</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>9.594494047619047</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.341517857142857</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.098214285714286</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.50483630952381</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.356026785714286</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>12.55003720238095</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1570,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.762046400951815</v>
+        <v>2577.551020408163</v>
       </c>
       <c r="D14" t="n">
-        <v>15.79685690926343</v>
+        <v>308.4148253713335</v>
       </c>
       <c r="E14" t="n">
-        <v>11.71890673404787</v>
+        <v>228.7977029028393</v>
       </c>
       <c r="F14" t="n">
         <v>1.347980427505884</v>
@@ -1065,16 +1589,57 @@
         <v>0.3405231499311667</v>
       </c>
       <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.259300595238095</v>
+      </c>
+      <c r="J14" t="n">
+        <v>18.39099702380952</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.26424319727891</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.5921303353658537</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.9419778963414634</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.7088097052845529</v>
+      <c r="M14" t="n">
+        <v>18.39099702380952</v>
+      </c>
+      <c r="N14" t="n">
+        <v>11.56436011904762</v>
+      </c>
+      <c r="O14" t="n">
+        <v>11.56063988095238</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9.427083333333332</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.738839285714286</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.908482142857143</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.259300595238095</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>10.71149553571428</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1650,76 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.714455681142177</v>
+        <v>2559.410430839002</v>
       </c>
       <c r="D15" t="n">
-        <v>15.64561275447287</v>
+        <v>305.4619633016132</v>
       </c>
       <c r="E15" t="n">
-        <v>11.71645539272122</v>
+        <v>228.7498433817001</v>
       </c>
       <c r="F15" t="n">
         <v>1.335353759311252</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3446954272265849</v>
+        <v>0.344695427226585</v>
       </c>
       <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.15327380952381</v>
+      </c>
+      <c r="J15" t="n">
+        <v>18.13244047619047</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8.022161989795917</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.5460175304878049</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.928734756097561</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.6995363313008131</v>
+      <c r="M15" t="n">
+        <v>18.13244047619047</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12.18005952380952</v>
+      </c>
+      <c r="O15" t="n">
+        <v>10.66034226190476</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>8.92485119047619</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.191964285714286</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.912202380952381</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.15327380952381</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1730,76 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.692742415229031</v>
+        <v>2551.133786848072</v>
       </c>
       <c r="D16" t="n">
-        <v>15.31497011824352</v>
+        <v>299.0065594514211</v>
       </c>
       <c r="E16" t="n">
-        <v>11.58440140398537</v>
+        <v>226.171646458762</v>
       </c>
       <c r="F16" t="n">
-        <v>1.322033792179777</v>
+        <v>1.322033792179778</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3585763705381012</v>
+        <v>0.3585763705381013</v>
       </c>
       <c r="H16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.082589285714286</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15.28459821428571</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.743629092261904</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.54296875</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.7828696646341464</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.6584095528455285</v>
+      <c r="M16" t="n">
+        <v>15.28459821428571</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12.67857142857143</v>
+      </c>
+      <c r="O16" t="n">
+        <v>10.60081845238095</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8.848586309523808</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.082589285714286</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.341889880952381</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.634114583333333</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>7.797929067460316</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1810,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.642772159428912</v>
+        <v>2532.086167800453</v>
       </c>
       <c r="D17" t="n">
-        <v>15.29476459724147</v>
+        <v>298.6120707080478</v>
       </c>
       <c r="E17" t="n">
-        <v>11.58440141561555</v>
+        <v>226.1716466858273</v>
       </c>
       <c r="F17" t="n">
         <v>1.320289590157367</v>
@@ -1182,16 +1829,57 @@
         <v>0.3568400788083703</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>0.672827743902439</v>
+        <v>1.212797619047619</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8052591463414634</v>
+        <v>15.72172619047619</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7390434451219512</v>
+        <v>6.223131613756614</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15.72172619047619</v>
+      </c>
+      <c r="N17" t="n">
+        <v>13.13616071428571</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>9.74516369047619</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8.714657738095237</v>
+      </c>
+      <c r="W17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.212797619047619</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.341889880952381</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.738095238095238</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>5.647852891156462</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1890,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.556811421772754</v>
+        <v>2499.319727891156</v>
       </c>
       <c r="D18" t="n">
-        <v>15.46722963379651</v>
+        <v>301.9792452312651</v>
       </c>
       <c r="E18" t="n">
-        <v>11.58440139817029</v>
+        <v>226.1716463452294</v>
       </c>
       <c r="F18" t="n">
         <v>1.335177287299411</v>
@@ -1221,16 +1909,60 @@
         <v>0.3444113781842588</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6955030487804879</v>
+        <v>1.177455357142857</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8061166158536586</v>
+        <v>15.73846726190476</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7508098323170732</v>
+        <v>6.633597883597883</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15.73846726190476</v>
+      </c>
+      <c r="N18" t="n">
+        <v>13.57886904761905</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9.317336309523808</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8.47470238095238</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.126488095238095</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.779017857142857</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.866629464285714</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>4.245256696428571</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +1973,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.492563950029744</v>
+        <v>2474.829931972789</v>
       </c>
       <c r="D19" t="n">
-        <v>15.53968239121321</v>
+        <v>303.3937990665436</v>
       </c>
       <c r="E19" t="n">
-        <v>11.52133343568662</v>
+        <v>224.9403194586436</v>
       </c>
       <c r="F19" t="n">
         <v>1.348774642966238</v>
@@ -1260,16 +1992,60 @@
         <v>0.337863925491401</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6872141768292683</v>
+        <v>1.160714285714286</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7897294207317074</v>
+        <v>15.41852678571428</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7384717987804879</v>
+        <v>7.448381696428571</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>15.41852678571428</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13.41703869047619</v>
+      </c>
+      <c r="O19" t="n">
+        <v>9.728422619047619</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8.258928571428571</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5.693824404761904</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.976190476190476</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.933407738095238</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.160714285714286</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>3.145461309523809</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +2056,73 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.326591314693635</v>
+        <v>2411.56462585034</v>
       </c>
       <c r="D20" t="n">
-        <v>15.38150477700117</v>
+        <v>300.3055694557372</v>
       </c>
       <c r="E20" t="n">
-        <v>11.45234741815707</v>
+        <v>223.5934495925903</v>
       </c>
       <c r="F20" t="n">
         <v>1.343087509955788</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3360330512295417</v>
+        <v>0.3360330512295416</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6634908536585367</v>
+        <v>1.160714285714286</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7922065548780488</v>
+        <v>15.46688988095238</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7278487042682927</v>
+        <v>7.448381696428571</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>15.46688988095238</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12.95386904761905</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.177083333333333</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9.415922619047619</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.001116071428571</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.160714285714286</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>9.227120535714285</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2133,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.116894705532421</v>
+        <v>2331.632653061224</v>
       </c>
       <c r="D21" t="n">
-        <v>15.06269824504852</v>
+        <v>294.0812514509473</v>
       </c>
       <c r="E21" t="n">
-        <v>11.09904785272552</v>
+        <v>216.6956961722601</v>
       </c>
       <c r="F21" t="n">
         <v>1.357116254017202</v>
@@ -1338,16 +2152,57 @@
         <v>0.3387936931432173</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6308117378048781</v>
+        <v>1.27046130952381</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7594321646341464</v>
+        <v>14.82700892857143</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6951219512195123</v>
+        <v>7.115885416666666</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14.82700892857143</v>
+      </c>
+      <c r="N21" t="n">
+        <v>12.31584821428571</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.113839285714286</v>
+      </c>
+      <c r="U21" t="n">
+        <v>9.038318452380953</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.381138392857142</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.989211309523809</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>6.191127232142857</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2212,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2234,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>2.591889880952381</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2251,90 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>2.174612032312925</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>1.591703869047619</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>1.40625</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>2.579985119047619</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>1.973084077380952</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/30/Filled_2D_sections/coronal/week30_coronal_Batch_Allmarks.xlsx
+++ b/measurements/30/Filled_2D_sections/coronal/week30_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2340,4 +2546,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week30_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2543.078231292516</v>
+      </c>
+      <c r="D10" t="n">
+        <v>68.67733930425938</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2331.632653061224</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2604.308390022676</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>307.3091238737106</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.08341332876932</v>
+      </c>
+      <c r="E11" t="n">
+        <v>294.0812514509473</v>
+      </c>
+      <c r="F11" t="n">
+        <v>315.21685952232</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.354150437848181</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01738062324191821</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.320289590157367</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.381697449151357</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3384914185912697</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.008292037179925594</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3285458072270827</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3585763705381013</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0119.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.7451598203705947</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.5026246899500346</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.019545822516343</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.9176629354822471</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>48</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.53876798115079</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.337184895621577</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.728422619047619</v>
+      </c>
+      <c r="F48" t="n">
+        <v>20.87983630952381</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>45</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.487640542328043</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.957910416575803</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.113839285714286</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.74516369047619</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>60</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.107328869047619</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6112616756548602</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.078869047619047</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.191964285714286</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>